--- a/fix-main/ig/StructureDefinition-tddui-related-person-contact-description.xlsx
+++ b/fix-main/ig/StructureDefinition-tddui-related-person-contact-description.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:28:11+00:00</t>
+    <t>2026-06-29T12:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-main/ig/StructureDefinition-tddui-related-person-contact-description.xlsx
+++ b/fix-main/ig/StructureDefinition-tddui-related-person-contact-description.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:38:54+00:00</t>
+    <t>2026-06-29T13:00:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
